--- a/data/opus_prometheus.xlsx
+++ b/data/opus_prometheus.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:Q98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +484,36 @@
           <t>Feedback</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>BERTScore</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>COMET-22</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BLEURT</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>BLEU</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>chrF++</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TER (inv)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -537,6 +567,24 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning while maintaining a modern Italian syntax. The archaic terms have been appropriately converted into their contemporary equivalents, such as "ben fatta" to "ben condotta" and "prode" to "valoroso." The use of "eccetera" instead of "etc." shows attention to cultural adaptation. However, there are minor issues with the flow, particularly in the transition between sentences, which could be smoother. The translation captures the essence of the original but occasionally leans towards a slightly mechanical rendering, especially in the description of Aiace's attributes. While the translation is generally accurate and comprehensible, it lacks the nuanced expression that would elevate it to the highest level of excellence. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L2" t="n">
+        <v>0.8466</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2233</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.3625</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -590,6 +638,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic terms have been appropriately converted into contemporary language, such as "pigli vendetta" to "si vendica" and "perdoni" to "non perdona." The sentence structure has been simplified to match modern Italian conventions, yet it retains the original's gravity and formality. The translation successfully conveys the legal and moral implications of the original text, preserving the essence of the medieval context while making it accessible to today's readers. The choice of words like "prescrive" instead of "dice" shows a nuanced understanding of the legal terminology. The translation is both accurate and natural, demonstrating the ability to balance historical authenticity with modern readability.</t>
         </is>
       </c>
+      <c r="L3" t="n">
+        <v>0.8048999999999999</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7437</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -643,6 +703,18 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning while maintaining a modern Italian syntax. The phrase "non fu dotato di minore forza d’animo" effectively captures the essence of the original "fue ornato Ponzio Aufidiano," preserving the subject's honor and dignity. The use of "cavaliere romano" instead of "romano cavaliere" shows a nuanced understanding of word order in modern Italian. The translation successfully conveys the original's formal tone and respect for the subject, though it could have been more elegant in rendering the concept of "forza d’ animo." The text flows naturally and would be easily understood by contemporary readers, indicating a good balance between fidelity to the original and accessibility in the target language.</t>
         </is>
       </c>
+      <c r="L4" t="n">
+        <v>0.8663</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.6349</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -696,6 +768,18 @@
           <t>The translation captures the essence of the original text but exhibits several issues that prevent it from achieving a higher score. The phrase "volontà comune" is a somewhat awkward rendering of "piace a tutti," and "circostanze richiedono" is a literal translation that doesn't fully capture the idiomatic nature of "tempo ha bisogno." Additionally, the term "guida" for "cavaliere" loses the historical connotation of the original text. While the translation remains comprehensible, it lacks the natural flow and precision expected of a high-quality translation. The use of "non mi opporrò" instead of "non riterrò" misses the opportunity to maintain the archaic tone while still being accessible to modern readers. The translation is functional but falls short of being elegant or culturally sensitive to the original's context.</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.6611</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4573</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -749,6 +833,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The phrase "parlare in modo appropriato" effectively captures the concept of "dicere appostatamente," though it could have been more precise. The use of "convincere" instead of "credere" slightly alters the nuance of the original, but it remains faithful to the core message. The translation successfully conveys the idea of deception through speech, though it loses some of the archaic flavor of the original. While the translation is clear and comprehensible, it doesn't fully capture the stylistic elements of the medieval text, making it read more like a modern interpretation rather than a direct translation. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>0.8185</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6104000000000001</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5894</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -794,6 +890,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic terms "ventipiovoli" and "risolute" are appropriately replaced with "scrosci di pioggia" and "dissolte," respectively, preserving the poetic imagery. The phrase "stia precipitando" effectively captures the original's sense of falling, though it could have been more elegant. The translation successfully conveys the metaphorical nature of the original, making it accessible to contemporary readers while retaining the essence of the medieval style. The sentence structure flows naturally, though there is room for improvement in the expression of the final clause.</t>
         </is>
       </c>
+      <c r="L7" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6772</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5989</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -843,6 +951,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully renders it into modern Italian while maintaining the original's tone and meaning. The use of "coloro" instead of "costoro" shows a nuanced understanding of the archaic forms, and the phrase "digrignano i denti" effectively captures the original's vivid imagery. The syntax flows naturally in modern Italian, preserving the rhetorical force of the original. The translation avoids literal translations and instead opts for idiomatic expressions that resonate with contemporary readers. The careful attention to the original's emotional intensity and the preservation of the rhetorical question at the end exemplify a high-quality translation that reads as if it were originally written in modern Italian.</t>
         </is>
       </c>
+      <c r="L8" t="n">
+        <v>0.8536</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5854</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -892,6 +1012,18 @@
           <t>The translation is a clear attempt to convey the original message but falls short in several aspects. While it maintains the basic structure of the sentence, it fails to capture the nuanced meaning of "vendimenti" and "presure," which are crucial elements of the original text. The translation uses "beni" instead of "vendimenti," which changes the meaning from transactions to ownership, and "pressioni" instead of "presure," which alters the concept of insurance to pressure. Additionally, the phrase "causò la vendita" is a literal translation that doesn't reflect the idiomatic nature of the original text. The syntax is overly simplified, losing the historical and cultural context of the original. The translation lacks the sophistication and depth required for a higher score, making it read more like a machine translation than a human-rendered text. So the overall score is 2.</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>0.8198</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.6506</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3914</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -941,6 +1073,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian text's meaning while maintaining modern readability. The use of "colui" instead of "quello" and "rispettato" instead of "onorabile" shows careful consideration of the original's tone. The phrase "per le sue grandi colpe" effectively captures the concept of "gran reità," though it could have been more elegant. The syntax flows naturally in modern Italian, preserving the original's gravity and formality. The translation successfully conveys the emotional weight of the original, particularly in the final clause about "empietà." While there's room for refinement in word choice, the translation achieves its communicative purpose with clarity and precision.</t>
         </is>
       </c>
+      <c r="L10" t="n">
+        <v>0.8451</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.7836</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.7071</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -994,6 +1138,18 @@
           <t>The translation is a direct word-for-word rendering of the original text, resulting in a sentence structure that is awkward and unnatural in modern Italian. The use of "rimanendo" instead of a more idiomatic expression such as "trovando" or "trovando che" makes the text feel mechanical and stiff. The phrase "nella menzogna" is a literal translation of "bugia," which is not the most appropriate term in this context. The translation lacks the fluidity and natural flow that characterizes a high-quality translation, making it read like a machine-generated text rather than a human translation. The syntax is rigid and fails to capture the poetic nature of the original text.</t>
         </is>
       </c>
+      <c r="L11" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.8232</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1043,6 +1199,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic term "dieci compagni" is appropriately rendered as "dieci compagni," preserving the historical context. The phrase "studiosamente si riservò" is effectively transformed into "con attenzione e prudenza," capturing the essence of the original while using natural modern Italian expressions. The translation successfully balances the need for clarity with the preservation of the original's formal tone, though it could have been more elegant in expressing the concept of "studiosamente." The sentence structure flows naturally, making it accessible to contemporary readers while respecting the source material's dignity.</t>
         </is>
       </c>
+      <c r="L12" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5326</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1092,6 +1260,18 @@
           <t>The translation is a direct word-for-word conversion of the archaic Italian phrase into modern Italian, which results in a text that is both grammatically incorrect and semantically imprecise. The use of "che" instead of "che'" indicates a misunderstanding of the archaic language structure, while the omission of the verb "erano" changes the tense and thus the meaning of the original text. Furthermore, the phrase "sapevo essere state" is awkwardly constructed and fails to capture the nuance of the original text, which implies a more passive knowledge. The translation lacks the necessary context and fails to convey the full meaning of the original text, making it difficult for readers to understand the intended message. So the overall score is 1.</t>
         </is>
       </c>
+      <c r="L13" t="n">
+        <v>0.7997</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.8438</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6235000000000001</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1145,6 +1325,18 @@
           <t>The translation is a direct word-for-word conversion of the archaic Italian text into modern Italian, resulting in a text that is both grammatically incorrect and semantically inaccurate. The use of "condusse" instead of "ha portato" fails to capture the idiomatic expression of "menò sua vita" and introduces a false sense of agency that wasn't present in the original. Additionally, the phrase "più bassa e più viziosa" is a literal translation that doesn't reflect the nuanced meaning of the original text, which suggests a more complex relationship between the two adjectives. The syntax is awkward and the text lacks the natural flow of a human translation, making it appear as if it was generated by a machine without any human oversight. So the overall score is 1.</t>
         </is>
       </c>
+      <c r="L14" t="n">
+        <v>0.8409</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.5984</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1198,6 +1390,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message. The use of "merzé" as a parenthetical explanation shows an effort to clarify the term while maintaining the text's integrity. The modernization of the syntax is handled well, with the phrase "Allo stesso modo" effectively replacing the archaic "Altressì". However, there is room for improvement in the rendering of "ragioni molte," which could have been more elegantly expressed. The translation is readable and natural, though it occasionally leans towards a slightly mechanical construction. The balance between preserving the original's flavor and adapting it to modern Italian is generally successful, but not quite reaching the highest level of sophistication. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>0.8485</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.6793</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.7071</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1247,6 +1451,18 @@
           <t>The translation is generally correct and comprehensible, but it lacks the nuance and sophistication of the original text. The phrase "misai in disordine" is a literal translation of "scapigliai," which doesn't capture the poetic nature of the original. The use of "capelli" instead of "signora" misses the cultural context of the time period. While the translation is understandable, it doesn't fully convey the emotional depth and historical flavor of the original. The syntax is modern but somewhat rigid, and the choice of words is functional rather than elegant. The translation would benefit from more idiomatic expressions and a better grasp of the cultural context. So the overall score is 3.</t>
         </is>
       </c>
+      <c r="L16" t="n">
+        <v>0.8048999999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5359</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1296,6 +1512,18 @@
           <t>The translation is a direct word-for-word conversion of the archaic Italian text into modern Italian, resulting in a text that is both grammatically incorrect and semantically inaccurate. The phrase "colui del quale" is incorrectly translated as "colui del quale," which is redundant and fails to capture the intended meaning of "that person who." Furthermore, the use of "erano" instead of "era" is a clear error, as it changes the singular subject to plural, altering the meaning of the original text. The translation also lacks the necessary punctuation and articles, making it difficult to read and understand. The text does not convey the emotional nuance of the original, which was about someone being in mourning for their lover. Instead, it presents a confusing and grammatically flawed sentence that fails to communicate the intended message. So the overall score is 1.</t>
         </is>
       </c>
+      <c r="L17" t="n">
+        <v>0.7448</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.5611</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1345,6 +1573,18 @@
           <t>The translation captures the essence of the original text but exhibits several issues that prevent it from achieving a higher score. While it maintains the basic meaning, the use of "non conoscevano" instead of "sapeano" fails to fully capture the archaic tone of the original. Additionally, the phrase "di coloro della congiura" is a direct translation that lacks the idiomaticity of the original, making it sound somewhat mechanical. The sentence structure follows the original too closely, resulting in a slightly awkward construction that doesn't flow naturally in modern Italian. The translation also misses the opportunity to employ more sophisticated modern equivalents that would better reflect the historical context. So the overall score is 3.</t>
         </is>
       </c>
+      <c r="L18" t="n">
+        <v>0.8695000000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.4368</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1394,6 +1634,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message. The use of modern Italian syntax while maintaining the formal tone of the original text shows a good balance between accessibility and authenticity. The translation of "hoste troiano" to "ospite troiano" is particularly effective, preserving the cultural reference while making it comprehensible to contemporary readers. The phrase "fa' che sia raccomandato a te, al mio posto" captures the essence of the original request, though there's room for minor refinement in the expression of the conditional mood. The translation is fluid and natural, with only slight mechanical traits that don't impede comprehension. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L19" t="n">
+        <v>0.8146</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.6137</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1447,6 +1699,18 @@
           <t>The translation is generally correct and comprehensible, maintaining the basic meaning of the original text. However, it shows some mechanical traits in its construction, particularly in the use of "fu scoperta" which is a somewhat literal rendering of "ripresa" and lacks the nuance of the original. The phrase "nel medesimo tempo" is a direct translation of "in simile bugìa," which doesn't capture the full connotation of the original text. While the translation is functional, it doesn't fully convey the historical and cultural context of the original, making it read more like a machine translation than a human-rendered text. The syntax is modern but lacks the sophistication and elegance expected in a high-quality translation. So the overall score is 3.</t>
         </is>
       </c>
+      <c r="L20" t="n">
+        <v>0.8711</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.7899</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1496,6 +1760,18 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning while maintaining a modern Italian syntax. The archaic terms "iniquità" and "malavventurata" are appropriately rendered as "ingiustizia" and "sfortunata," respectively, preserving the original sentiment while using contemporary language. The sentence structure flows naturally, and the emotional weight of the original is effectively conveyed through the use of "piangevano" instead of a more literal translation of "ripiagnevano." The translation successfully captures the essence of the original text without resorting to awkward or mechanical language, though it could have been slightly more elegant in expressing the relationship between the father and the girl.</t>
         </is>
       </c>
+      <c r="L21" t="n">
+        <v>0.8058</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.6372</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1549,6 +1825,18 @@
           <t>The translation captures the essence of the original text but exhibits several issues that prevent it from achieving a higher score. The phrase "certamente ebbi" is a direct translation of "certainio io ebbi," which is not idiomatic in modern Italian. Additionally, "mi dolevo" is a literal translation of "mi dolfi," which doesn't convey the same emotional weight as the original. The use of "disprezzata" instead of "schifata" loses the colloquial tone of the original text. While the translation is comprehensible, it lacks the natural flow and nuance of a high-quality translation, making it read more like a machine translation than a human-rendered text.</t>
         </is>
       </c>
+      <c r="L22" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.6205000000000001</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.5413</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1598,6 +1886,18 @@
           <t>The translation demonstrates a clear attempt to modernize the archaic Italian text while maintaining its essence. However, it shows some mechanical traits in the rendering of certain phrases. For instance, "per l'audacia" is a literal translation of "per l'ardire," which could have been expressed more naturally as "per l'audacia." Additionally, the use of "qualcun altro" instead of "gli altri" introduces a slight shift in meaning, making the translation less precise than ideal. While the overall message is preserved, the translation lacks the nuanced expression of the original, particularly in the rendering of "provedenzia," where "prudenza" is used without capturing the full connotation of divine providence. The syntax is generally correct but occasionally feels slightly rigid, indicating a translation that, while functional, doesn't fully capture the stylistic richness of the original.</t>
         </is>
       </c>
+      <c r="L23" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1651,6 +1951,18 @@
           <t>The translation is generally accurate and maintains the basic meaning of the original text. However, it uses "condusse" instead of the more appropriate "trasse," which is a slight deviation from the source text's archaic style. The phrase "con sé" is a literal translation of "seco," which could have been expressed more naturally as "con loro." While the translation is comprehensible and follows modern Italian syntax, it lacks the nuanced expression of the original text and doesn't fully capture the historical context. The use of "dei" instead of "di" is also a minor error that affects the authenticity of the translation. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L24" t="n">
+        <v>0.9543</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.8736</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.8699</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1700,6 +2012,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian text and successfully renders it into modern Italian while maintaining readability. The use of "non lo volle riconoscere" instead of "non voleva conoscerlo" shows a nuanced understanding of the original's intent, preserving the passive voice which was crucial in the source text. The term "colei" for "quella" is particularly apt, as it reflects the formal tone of the original. The phrase "diede coraggio" captures the essence of "diede ardire" effectively, though there could have been a more elegant way to express this. The syntax flows naturally in modern Italian, and the translation maintains the authoritative tone of the original. While the translation is generally excellent, it lacks the perfect refinement seen in a score 5 translation, such as the omission of "per" before "nimico" which was present in the original. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L25" t="n">
+        <v>0.8517</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.7909</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.5589</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1749,6 +2073,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully renders it into modern Italian while maintaining the original meaning. The use of "coraggio" instead of "ardire" shows a good adaptation to contemporary language, though it could have been more precise. The phrase "non avrebbe avuto questo spirito" captures the essence of the original "avevano questo animo," but the choice of "spirito" might be slightly less accurate than "mente." The syntax flows naturally, and the translation is free of obvious errors or awkward constructions. While the translation is competent and clear, it lacks the exceptional precision and nuance that would elevate it to the highest score. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L26" t="n">
+        <v>0.8225</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1798,6 +2134,18 @@
           <t>The translation is mechanically correct but lacks the nuance and style of the original text. The phrase "ragionevolmente" is a direct translation of "reasonably," which is too literal and fails to capture the rhetorical tone of the original. The word "interpretato" is used instead of the more appropriate "interpretato come," which would better reflect the medieval context. The sentence structure is overly simplified and doesn't convey the sophisticated nature of the original text. The translation misses the opportunity to use more idiomatic expressions that would make it sound more natural in modern Italian. So the overall score is 2.</t>
         </is>
       </c>
+      <c r="L27" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.7207</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.4953</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1847,6 +2195,18 @@
           <t>The translation maintains the basic meaning of the original text but exhibits several issues. The phrase "perdonava più di tutti gli altri" is awkwardly constructed and lacks the elegance of the original "sopra tutti gli altri." The use of "potete credere con maggior sicurezza" is too literal and fails to capture the idiomatic nature of "a cui più sicuramente possiate credere." Additionally, the word "comandante" is a modern term that doesn't reflect the archaic context of the original text. The syntax is choppy and lacks the flow of the original, making it read more like a machine translation than a human-rendered text. The translation also misses the nuance of the original's authoritative tone, which is diminished by the overly simplified rendering.</t>
         </is>
       </c>
+      <c r="L28" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.8403</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.6935</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1896,6 +2256,18 @@
           <t>The translation is generally accurate and comprehensible, maintaining the core meaning of the original text. However, it exhibits some mechanical qualities, particularly in the use of "poiché" which feels slightly forced compared to the more natural "con ciò". The phrase "abbia scritto" is a somewhat literal rendering of "scrivesse", missing the opportunity to employ a more idiomatic expression such as "scrisse". While the translation is functional, it lacks the nuanced flow and stylistic sophistication expected of a higher-quality translation. The text remains readable but doesn't fully capture the historical and literary richness of the original. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L29" t="n">
+        <v>0.8994</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.7255</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1945,6 +2317,18 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning while maintaining a modern Italian syntax. The archaic terms have been appropriately converted into their contemporary equivalents, such as "usatissima" to "frequentemente usata" and "incommutabile" to "incorruttibile". The translation successfully preserves the logical flow of the original, using appropriate connecting phrases like "se non fosse" and "invece". However, there are minor issues with the phrasing, such as the somewhat literal rendering of "posto che" as "dato che", which could have been expressed more naturally. The translation also slightly simplifies the original's complexity, particularly in the final clause, though this doesn't significantly impact the overall quality. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L30" t="n">
+        <v>0.8057</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1998,6 +2382,18 @@
           <t>The translation maintains the basic meaning of the original text but shows several issues. The use of "immediatamente" instead of "immanente" fails to capture the archaic tone of the original text, making it sound too modern and less formal. The phrase "ostacolare il passaggio" is a literal translation that doesn't reflect the medieval context of "contradiare il passamento." Additionally, the sentence structure follows a modern pattern rather than maintaining the archaic style of the original. While the translation is comprehensible, it lacks the stylistic elements that would make it more authentic to the medieval period. The choice of words such as "presenza" and "cavalieri" are not particularly problematic, but they don't contribute to the historical accuracy of the translation. So the overall score is 3.</t>
         </is>
       </c>
+      <c r="L31" t="n">
+        <v>0.8359</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2047,6 +2443,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully renders it into modern Italian while maintaining the original's tone and meaning. The use of "con grande stupore" effectively captures the sense of "meravigliandose" and "fortemente," preserving the emotional weight of the original text. The phrase "vi prego di dirmi" is a natural and idiomatic way to express the request, showing a good understanding of modern Italian expressions. The translation also appropriately adapts the formal address "messer" to "Messer," which is a common practice in modern Italian translations of classical texts. The syntax flows naturally, and there are no awkward constructions or literal translations that would indicate a machine-generated text. So the overall score is 5.</t>
         </is>
       </c>
+      <c r="L32" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.8234</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.5923</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2096,6 +2504,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message. The use of "messer" instead of "Signor" and "buon animo" instead of "di buona mente" shows a good understanding of the period-specific terminology. The sentence structure has been modernized while maintaining the original's essence, making it accessible to contemporary readers. The choice of "affinché" over "acciocché" reflects a nuanced understanding of the language evolution. The translation is both accurate and natural, preserving the formal tone of the original text. The modernization process is seamless, with no awkwardness or mechanical elements visible.</t>
         </is>
       </c>
+      <c r="L33" t="n">
+        <v>0.8858</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.8096</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.8121</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2149,6 +2569,18 @@
           <t>The translation demonstrates a clear misunderstanding of the original text's meaning and structure. The phrase "sanza fallo" was incorrectly interpreted as "senza dubbio," which completely changes the intended meaning. Furthermore, the term "porco salvatico" was mistranslated as "cinghiale selvatico," which is a significant error since "porco" refers to a wild boar, not a wild pig. Additionally, the syntax is awkward and unnatural, with phrases like "supera l’uomo nell’udito" being a literal translation that fails to capture the original's poetic nature. The translation lacks the archaic elements present in the original text, making it appear as if it were a modern, rather than medieval, text. The result is a text that is both linguistically incorrect and semantically inaccurate, failing to convey the original message effectively.</t>
         </is>
       </c>
+      <c r="L34" t="n">
+        <v>0.7549</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.2433</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2198,6 +2630,18 @@
           <t>The translation demonstrates a clear misunderstanding of the archaic Italian text, resulting in a significant loss of meaning. The phrase "si mandano lancioni" was incorrectly interpreted as "si inviano lance," which changes the original metaphorical meaning of thunder to a literal action of sending arrows. Furthermore, the term "capo di porco" was translated literally as "capo di porco" instead of the more appropriate "testa di maiale." This literal translation fails to capture the idiomatic nature of the original text, making it appear as if it were a machine-generated translation. The syntax is awkward and lacks the natural flow of modern Italian, indicating a lack of understanding of both the source language's nuances and the target language's conventions.</t>
         </is>
       </c>
+      <c r="L35" t="n">
+        <v>0.7233000000000001</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2247,6 +2691,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian text's meaning while maintaining modern readability. The choice of "cerbiatti" for "cerbi" and "cinghiale" for "cinghiare" shows careful consideration of the original's context and cultural references. The syntax flows naturally in modern Italian, preserving the original's poetic essence without feeling forced or mechanical. The translation successfully captures the original's imagery and tone, making it accessible to contemporary readers while respecting the source material's historical character. The use of "conosce bene" instead of "sa bene" adds a slight nuance that enhances the translation's modernity without losing the original's spirit.</t>
         </is>
       </c>
+      <c r="L36" t="n">
+        <v>0.7796</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.6082</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2296,6 +2752,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic terms "disidirosi" and "porco cenghiare" have been appropriately rendered as "timorosi" and "cinghiale," respectively, preserving the essence of the original. The sentence structure has been updated to contemporary Italian, making it accessible to modern readers while retaining the poetic quality of the original. The translation successfully balances the need for clarity with the preservation of the original's stylistic elements, though there is room for minor improvements in the expression of certain nuances.</t>
         </is>
       </c>
+      <c r="L37" t="n">
+        <v>0.7718</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.5468</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2349,6 +2817,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic term "incorporee" is appropriately rendered as "incorporee," preserving the historical nuance while remaining comprehensible. The phrase "non si trovano entro i corpi" effectively captures the concept of "non conversano intra lle corpora," though it could have been more elegant. The translation successfully conveys the relationship between the incorporeal and the divine, though it slightly simplifies the original's complexity. While the translation is generally accurate and readable, it lacks some of the stylistic sophistication found in a truly excellent translation, such as the use of more varied connecting phrases or a more nuanced rendering of the metaphorical language. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L38" t="n">
+        <v>0.8148</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.5863</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2398,6 +2878,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The phrase "si amministrano e si giudicano" effectively captures the concept of "dispensano e iudicano," preserving the original's intent without resorting to literal translation. The use of "per mezzo del quale" instead of "per la quale" shows a nuanced understanding of the medieval context, though it could have been more elegant. The translation successfully conveys the authoritative tone of the original while remaining accessible to contemporary readers. While the translation is competent and clear, it lacks the exceptional fluidity and depth that would warrant a perfect score.</t>
         </is>
       </c>
+      <c r="L39" t="n">
+        <v>0.8246</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.5939</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2447,6 +2939,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message. The use of "superava" instead of "passava" shows a nuanced understanding of the context, while "assegnato" appropriately captures the concept of "deputato". The syntax flows naturally in modern Italian, maintaining the formal tone of the original. The translation avoids literal translations and uses idiomatic expressions that are both accurate and accessible. The preservation of the original's rhetorical style and the careful attention to historical context make this translation particularly effective.</t>
         </is>
       </c>
+      <c r="L40" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.7354000000000001</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2496,6 +3000,18 @@
           <t>The translation maintains the archaic style of the original text while making it accessible to modern readers. The use of "retta" instead of "diritta" shows a careful consideration of the historical context, preserving the medieval tone while ensuring readability. The phrase "con virtù" is appropriately rendered as "con virtù," maintaining the original's emphasis on virtue. The translation successfully captures the philosophical concept of goodness ("il bene") without losing the original's nuanced meaning. The syntax flows naturally in modern Italian, demonstrating a balance between respecting the source material and adapting it for contemporary comprehension. The translation achieves a high level of precision and readability, making it indistinguishable from a translation by a highly qualified human.</t>
         </is>
       </c>
+      <c r="L41" t="n">
+        <v>0.8778</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.9052</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.7842</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2545,6 +3061,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully renders it into modern Italian while maintaining the original meaning. The use of "avvelenavano" instead of "invileno" shows a nuanced understanding of the verb choice, and "nel loro stesso veleno" captures the essence of "inazzi della loro salive" effectively. The sentence structure flows naturally in the target language, and the translation avoids awkward calques or literal translations. The preservation of the original's tone and style, along with the appropriate modernization, indicates a high level of competence in handling historical texts. The translation is both accurate and readable, making it indistinguishable from a translation by a highly qualified human.</t>
         </is>
       </c>
+      <c r="L42" t="n">
+        <v>0.7893</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.5313</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2590,6 +3118,18 @@
           <t>The translation demonstrates a clear misunderstanding of the archaic Italian text, resulting in a nonsensical rendering. The phrase "glel fai diretro" is incorrectly translated as "glielo metti dietro," which changes the meaning entirely. Furthermore, the use of "nel sedere" instead of "sul culo" is inappropriate and fails to capture the colloquial nature of the original. The syntax is awkward and the text lacks the fluidity required for a proper translation. The attempt to modernize the language results in a text that is neither accurate nor comprehensible, making it unusable for communication purposes. The translation shows no evidence of understanding the cultural context or the historical period of the original text, and the result is a text that bears no resemblance to the intended meaning.</t>
         </is>
       </c>
+      <c r="L43" t="n">
+        <v>0.8024</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2639,6 +3179,18 @@
           <t>The translation maintains the core meaning of the original text but introduces a slight shift in nuance by using "materiali" instead of "corporali," which could imply a more physical rather than spiritual aspect of vision. While the translation is comprehensible and follows modern Italian syntax, it lacks the poetic quality of the original and doesn't fully capture the archaic tone. The phrase "anche questa fu colpa tua" is a good adaptation of the original, but the use of "perché" instead of "però" makes the sentence flow less naturally in modern Italian. The translation is adequate but misses some of the stylistic elements that would make it more engaging and faithful to the original's literary style.</t>
         </is>
       </c>
+      <c r="L44" t="n">
+        <v>0.8411</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.8867</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.7471</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2692,6 +3244,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic terms have been appropriately converted into their contemporary equivalents, such as "ttu" to "tu" and "feriato" to "festivo." The translation successfully preserves the logical flow of the original, presenting three distinct reasons for not responding. However, there is a minor issue with the final word "rispondert," which could be more elegantly expressed as "rispondere" to maintain consistency with the rest of the text. The translation is fluent and comprehensible, though it lacks the nuanced historical flavor present in the gold translation. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L45" t="n">
+        <v>0.8803</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2741,6 +3305,18 @@
           <t>The translation is a good attempt at rendering the archaic Italian into modern Italian, maintaining the basic meaning of the original text. However, it shows some mechanical traits in the construction of the sentence, particularly in the use of "darsi" which could have been better expressed as "dare". The translation also loses some of the nuance of the original text by simplifying the concept of "grande avere" to just "una grande somma", which doesn't fully capture the original meaning. While the translation is comprehensible and conveys the general idea, it lacks the sophistication and elegance of a more refined translation. The syntax is modern but not entirely natural, and there's room for improvement in terms of idiomatic expression. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L46" t="n">
+        <v>0.7259</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.5422</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2790,6 +3366,18 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning while maintaining a modern Italian syntax. The archaic terms have been appropriately converted into contemporary language, such as "tradigione" to "tradimento" and "moneta" to "denaro." The sentence structure has been reorganized to fit modern Italian conventions, making it more accessible to today's readers. However, there are minor issues with the flow of the text, particularly in the transition between clauses, which could be smoother. The translation successfully conveys the moral lesson and the narrative elements of the original text, though it occasionally leans towards a slightly mechanical rendering of certain phrases. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L47" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.7211</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.5631</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2843,6 +3431,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian text while maintaining modern readability. The use of "per lui" instead of "a lui" shows a nuanced understanding of the language shift. The phrase "cosa vergognosa" effectively captures the moral connotation of "cosa sconcia." The syntax is appropriately modernized, yet it retains the gravity of the original. The translation successfully conveys the cause-and-effect relationship between the actions and their consequences, preserving the original's formal tone. The choice of "punizione" for "gastigamento" is particularly apt, showing sensitivity to the historical context. The text flows naturally without feeling like a direct translation, indicating a high level of linguistic competence.</t>
         </is>
       </c>
+      <c r="L48" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.6355</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2896,6 +3496,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian text's meaning while maintaining modern readability. The use of "soprattutto" instead of "massimamente" shows a nuanced understanding of the original's emphasis. The phrase "dandogli il regno" effectively captures the concept of "dando lui re," though it could have been more elegant. The rendering of "lunghissimamente" as "per molto tempo" is appropriate but slightly less precise than the original. The syntax flows naturally in modern Italian, preserving the original's essence while avoiding literal translations. The translation successfully conveys the historical context and maintains the formal tone of the original, though there's room for minor improvements in stylistic refinement.</t>
         </is>
       </c>
+      <c r="L49" t="n">
+        <v>0.8568</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.7461</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2949,6 +3561,18 @@
           <t>The translation is a clear attempt to modernize the archaic Italian text but falls short in several aspects. While it captures the basic meaning of the original, it fails to preserve the poetic and metaphorical nature of the source text. The phrase "in base alle caratteristiche" is too literal and lacks the nuance of "proprietate," which carries a deeper connotation of ownership or possession. Additionally, the use of "si unisce" instead of "congiunge" loses the formal tone of the original. The translation also omits the possessive pronoun "quello," which was present in the original text, thus changing the emphasis of the sentence. The overall result is a translation that is comprehensible but lacks the sophistication and elegance of the original, making it read more like a machine translation than a human-rendered text. So the overall score is 2.</t>
         </is>
       </c>
+      <c r="L50" t="n">
+        <v>0.8774</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.7185</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.6778999999999999</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2998,6 +3622,18 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning while maintaining a modern Italian syntax. The archaic terms are appropriately rendered into contemporary language, such as "non uniti" for "non in una carne" and "solo spirito" for "uno spirito". The use of "bensì" instead of "ma" shows a nuanced understanding of connecting ideas. However, there is room for improvement in the expression of the spiritual concepts, where the translation could have been more elegant. The phrase "con lui" at the end, while accurate, slightly deviates from the original's simplicity. The translation successfully conveys the core message but occasionally opts for slightly mechanical constructions, particularly in the final sentence. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L51" t="n">
+        <v>0.8717</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.8211000000000001</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.7086</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3047,6 +3683,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message. The use of "ve lo raccontiamo" instead of "il vi raccontiamo" shows a nuanced understanding of modern Italian syntax. The term "percepì" for "ebbe sentito" is a particularly apt choice, capturing the depth of the original experience. The phrase "la vera grandezza" effectively replaces "in grande," preserving the original's emphasis on authenticity. The translation maintains the poetic flow while being accessible to contemporary readers, though it could have been more faithful to the original's rhythm. The modernization of the text is handled with care, avoiding anachronistic expressions while preserving the essence of the original.</t>
         </is>
       </c>
+      <c r="L52" t="n">
+        <v>0.7747000000000001</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.5168</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3096,6 +3744,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic terms "dolore," "armi," and "fatica" are appropriately rendered into their modern equivalents, preserving the original's essence. The use of parentheses around "(gli uomini)" shows a thoughtful approach to potential ambiguity, though it could have been expressed more elegantly. The translation successfully captures the emotional weight of the original, particularly in the final comparison to sheep, which remains clear and impactful in the modern version. While the translation is generally excellent, there is room for minor improvements in the flow and expression of certain phrases. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L53" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3145,6 +3805,18 @@
           <t>The translation is a clear example of a machine-generated text, with a rigid and unnatural construction that fails to capture the original's archaic tone. The phrase "non provò fastidio" is a direct, literal translation that doesn't reflect the medieval context, while "ascoltare tali parole" is an awkward rendering of the original. The syntax is broken and lacks the necessary historical flavor, making it read like a modern text forced into an archaic context. The translation completely misses the nuance of the original text, which emphasizes the lack of Christ's interest in hearing the words. The use of "Cristo" instead of "il Signore" or "il Cristo" further demonstrates the lack of attention to historical accuracy and cultural sensitivity. The text is not only mechanically translated but also fails to convey the original's meaning and style, making it unsuitable for any serious use.</t>
         </is>
       </c>
+      <c r="L54" t="n">
+        <v>0.7845</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3194,6 +3866,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message. The use of "costoro" instead of "loro" and "stento" instead of "malapena" shows careful attention to modern Italian equivalents while maintaining the historical tone. The syntax flows naturally, and the translation avoids awkward constructions, making it accessible to contemporary readers. The preservation of the original's formal register and the careful selection of modern terms indicate a high level of linguistic competence. The translation is both accurate and stylistically appropriate, reflecting the source text's dignity and precision.</t>
         </is>
       </c>
+      <c r="L55" t="n">
+        <v>0.8199</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3243,6 +3927,18 @@
           <t>The translation captures the essence of the original text but exhibits several issues that prevent it from achieving a higher score. While it maintains the basic meaning, the phrase "nel modo, nel tempo e nella misura" is a literal translation that doesn't reflect the idiomatic nature of the original text. The use of "annusare" instead of "profumare" is a slight deviation from the original "odorare," which could have been better preserved. Additionally, the structure "e" is used twice, which is less elegant than the original "et." The translation is comprehensible but lacks the natural flow and nuance of a high-quality translation. The modernization of the text is adequate but not fully successful in capturing the poetic and archaic tone of the original.</t>
         </is>
       </c>
+      <c r="L56" t="n">
+        <v>0.7212</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.4652</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3292,6 +3988,18 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning while maintaining a modern Italian syntax. The archaic term "albergo" is appropriately replaced with the contemporary "alloggio," showing sensitivity to language evolution. The phrase "come s'egli andasse pensando" is elegantly transformed into "come se stesse riflettendo," preserving the original's contemplative tone while using natural modern Italian. The translation successfully conveys the original's atmosphere and intent without resorting to literal translations or awkward constructions. The choice of words and sentence structure feels organic rather than mechanical, indicating a high level of fluency and readability.</t>
         </is>
       </c>
+      <c r="L57" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.9045</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.7963</v>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3341,6 +4049,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully renders it into modern Italian while maintaining the original's poetic essence. The use of "desideroso" for "disioso" and "recarmi" for "andare" shows careful attention to semantic equivalence and modern Italian vocabulary. The syntax flows naturally, and the translation captures the original's contemplative tone without resorting to literal translations. The choice of "vi volo" for "volo lì" preserves the original's metaphorical expression while remaining accessible to contemporary readers. The translation achieves a balance between respecting the source text's style and ensuring readability in modern Italian, making it indistinguishable from a translation by a highly qualified human.</t>
         </is>
       </c>
+      <c r="L58" t="n">
+        <v>0.8443000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.6222</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3390,6 +4110,18 @@
           <t>The translation is generally correct and comprehensible, maintaining the basic meaning of the original text. However, it lacks the fluidity and naturalness expected of a higher-quality translation. The use of "subito" instead of "all'improvviso" makes the text sound slightly more contemporary than the original, which was written in archaic Italian. Additionally, the phrase "tutta quella moltitudine" is a somewhat mechanical rendering of "tutta questa turba," missing the poetic nuance of the original. While the translation is serviceable, it doesn't fully capture the stylistic richness of the medieval text, making it read like a translation rather than an original piece. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L59" t="n">
+        <v>0.8122</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.8764</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3439,6 +4171,18 @@
           <t>The translation demonstrates a clear misunderstanding of the original text's meaning and structure. The phrase "sa dare un giudizio vero" is a literal translation of "sa rendere vero giudicio," which is incorrect in both grammar and semantics. The use of "conosce" instead of "vede" changes the subject of the sentence, altering the original meaning. Furthermore, the omission of "tutte le cose" in the second part of the sentence results in a significant loss of information. The syntax is awkward and the translation fails to capture the archaic nature of the original text while attempting to modernize it. The result is a text that neither preserves the original meaning nor achieves the intended modernization, making it unsuitable for any purpose.</t>
         </is>
       </c>
+      <c r="L60" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.7224</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.5044999999999999</v>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3488,6 +4232,18 @@
           <t>The translation is a direct word-for-word rendering of the original text, which results in a sentence structure that is awkward and unnatural in modern Italian. The use of "fino a che punto" instead of a more idiomatic expression such as "quanto" or "come" fails to capture the poetic nature of the original text. Additionally, the phrase "a causa della sua superbia" is a literal translation that doesn't reflect the nuanced meaning of "superbia" in this context. The syntax is rigid and lacks the fluidity expected in a high-quality translation. The text reads like it was generated by a machine, with no attempt to adapt the language to contemporary Italian conventions or to preserve the original's stylistic elements. So the overall score is 2.</t>
         </is>
       </c>
+      <c r="L61" t="n">
+        <v>0.7993</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.6707</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3537,6 +4293,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic term "Gorgone" is preserved appropriately, and the phrase "e ho questa caratteristica" effectively conveys the original's "e ho questa proprietà." The use of "proprio come" instead of "sì come" shows a nuanced understanding of the original's intent, though it could have been more faithful to the original's phrasing. The translation successfully adapts the medieval expression into contemporary Italian while preserving the essence of the original text. The sentence structure is clear and natural, making it accessible to modern readers. While the translation is competent and communicates the message effectively, it lacks the exceptional fluidity and precision that would warrant a perfect score. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L62" t="n">
+        <v>0.8829</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.8234</v>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3586,6 +4354,18 @@
           <t>The translation is severely flawed and fails to convey the original message. The archaic term "matricola" is completely omitted, which is crucial to the meaning of the text. The sentence structure is broken and lacks proper punctuation, making it difficult to understand. The use of commas instead of proper conjunctions ("e") shows a lack of understanding of Italian grammar rules. The translation also omits the word "quando," which is essential to the temporal aspect of the original text. The text is nonsensical and fails to provide any meaningful information about the original content. It appears to be a crude attempt at translation, likely produced by a faulty automatic system.</t>
         </is>
       </c>
+      <c r="L63" t="n">
+        <v>0.8608</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.7698</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.5888</v>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3635,6 +4415,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully renders it into modern Italian while maintaining the original's tone and meaning. The choice of "ribadisco" instead of "rido" captures the essence of the original "ridico" while being more appropriate for the modern context. The phrase "secondo il tuo insegnamento" effectively conveys the concept of "comandamento," showing a nuanced understanding of the relationship between the speaker and the subject matter. The syntax flows naturally, and the translation avoids any awkwardness or mechanical elements, making it indistinguishable from a human translation. The preservation of the original's respectful tone towards Saint Augustine is particularly well-handled, demonstrating both linguistic competence and cultural sensitivity. So the overall score is 5.</t>
         </is>
       </c>
+      <c r="L64" t="n">
+        <v>0.8208</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.5901</v>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3688,6 +4480,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message. The modernization of terms such as "faccendole" to "imprese" and "sesso" to "se" shows careful consideration of contemporary usage while maintaining the historical context. The syntax flows naturally in modern Italian, and the translation captures the ceremonial tone of the original text. The use of "degne di memoria" instead of a more literal translation of "di maggiore memoria" reflects a nuanced understanding of the text's purpose. The translation avoids awkward constructions and presents a coherent narrative that would be easily understood by modern readers.</t>
         </is>
       </c>
+      <c r="L65" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.5243</v>
+      </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3737,6 +4541,18 @@
           <t>The translation captures the essence of the original text but exhibits some mechanical traits. The phrase "a causa del" is a direct calque from the source text, indicating a somewhat rigid approach to translation. While the overall meaning is preserved, the expression "vedendo le sue lodi" feels slightly awkward in modern Italian, suggesting a literal translation rather than a more idiomatic rendering. The use of "tu" instead of "si" introduces a slight shift in the formal register, which could have been better handled to maintain consistency with the original's tone. The translation is comprehensible and conveys the basic message, but lacks the natural flow and elegance expected in high-quality translations.</t>
         </is>
       </c>
+      <c r="L66" t="n">
+        <v>0.8401</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.7392</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.4859</v>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3786,6 +4602,18 @@
           <t>The translation is a simplified version of the original text, losing the archaic nature of the source material. While it conveys the basic information about Saint Augustine and his book, it fails to capture the medieval style and the specific reference to the book's title. The use of "scrisse" instead of "fece" is a significant departure from the original text's tone, making it sound more modern than intended. Additionally, the omission of "della" before "Città di Dio" changes the meaning and the historical context of the original text. The translation lacks the nuance and precision required for a higher score, as it doesn't maintain the original's archaic elements while still being comprehensible in modern Italian. So the overall score is 2.</t>
         </is>
       </c>
+      <c r="L67" t="n">
+        <v>0.8744</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.8859</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.6618000000000001</v>
+      </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3835,6 +4663,18 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning while maintaining a modern Italian syntax. The phrase "non ho mai sentito dire" effectively captures the archaic "Non udii mai che egli avesse," preserving the original's intent without sounding overly formal. The term "limitare" for "stringere a legge" is a suitable modern equivalent that conveys the same concept while being accessible to contemporary readers. The translation successfully balances archaic elements with modern language, making it both authentic and comprehensible. The sentence structure flows naturally, and there are no awkward constructions or unnatural expressions. The translation achieves the goal of rendering the medieval text into modern Italian while retaining its essence and clarity.</t>
         </is>
       </c>
+      <c r="L68" t="n">
+        <v>0.8878</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.6541</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.6163999999999999</v>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3888,6 +4728,18 @@
           <t>The translation provided is a direct copy of the source text without any attempt at modernization or adaptation. It fails to convey the intended meaning of the original text, which was to translate it into modern Italian while preserving the archaic elements. The response shows no effort to make the text accessible to contemporary readers, and it lacks any indication of understanding the task requirements. The translation is completely devoid of any linguistic or historical context, making it impossible to comprehend the original message. It also does not follow the instruction to provide a modern translation of the archaic text. So the overall score is 1.</t>
         </is>
       </c>
+      <c r="L69" t="n">
+        <v>0.8117</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.6675</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.7274</v>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3937,6 +4789,18 @@
           <t>The response demonstrates a complete failure to understand and translate the original text. The translation is nonsensical and lacks any connection to the source material. The text is filled with grammatical errors and does not convey the intended meaning of the original. The sentence structure is broken and the vocabulary used is inappropriate for the context. The translation fails to capture any of the original text's nuances or historical context, making it unusable for any purpose. The response shows no evidence of human intervention or understanding of the source language. So the overall score is 1.</t>
         </is>
       </c>
+      <c r="L70" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3986,6 +4850,18 @@
           <t>The response is a direct copy of the original text without any attempt at translation or adaptation. It fails to provide a modern Italian equivalent for the archaic terms and maintains the same syntactic structure as the source text. The text lacks any meaningful transformation into contemporary Italian language, making it completely unusable for modern readers. The translation shows no evidence of understanding the source material or attempting to convey its meaning in a comprehensible way. It is essentially a word-for-word rendering that does not meet the basic requirements of translation, rendering the text indistinguishable from the original source. So the overall score is 1.</t>
         </is>
       </c>
+      <c r="L71" t="n">
+        <v>0.8142</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.6891</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4035,6 +4911,18 @@
           <t>The translation is a direct word-for-word conversion of the archaic Italian text into modern Italian, resulting in a text that is both grammatically incorrect and semantically inaccurate. The phrase "sì affrettati" is incorrectly translated as "così affrettati," which changes the meaning of the original text. Additionally, the use of "dovete" instead of "sappiate" fails to capture the formal tone of the original text. The syntax is awkward and unnatural, making it difficult to understand the intended message. The translation lacks the necessary cultural and historical context, and the language used is inappropriate for the intended audience. So the overall score is 1.</t>
         </is>
       </c>
+      <c r="L72" t="n">
+        <v>0.8178</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.8482</v>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4080,6 +4968,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian text and successfully conveys the original message in modern Italian. The syntax is clear and natural, with appropriate use of modern Italian expressions such as "popolo acheo" instead of "gente achea". The translation maintains the original's formal tone while being accessible to contemporary readers. The archaic terms are accurately rendered, preserving the historical context without compromising readability. The sentence structure flows smoothly, and the translation captures the emotional weight of the original text, particularly in the expression of shame and honor. The translation achieves a balance between fidelity to the source and the needs of the target language, making it indistinguishable from a translation by a highly qualified human.</t>
         </is>
       </c>
+      <c r="L73" t="n">
+        <v>0.8384</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.5438</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4133,6 +5033,18 @@
           <t>The translation captures the essence of the original text while maintaining a modern Italian syntax. The archaic terms have been appropriately replaced with their contemporary equivalents, such as "acconciamento" to "intento," "Idio" to "Dio," and "proximo" to "prossimo." The phrase structure follows a logical progression, preserving the original's intent to perform great deeds while emphasizing peace and love. The translation successfully conveys the medieval context in a way that remains accessible to modern readers, though it could benefit from a more nuanced rendering of certain terms to fully capture the historical flavor of the original. The text flows naturally and reads as if it were originally written in modern Italian, demonstrating a high level of translation quality.</t>
         </is>
       </c>
+      <c r="L74" t="n">
+        <v>0.7358</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.2108</v>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4182,6 +5094,18 @@
           <t>The translation is generally correct and comprehensible, maintaining the core message of the original text. However, it shows some mechanical traits in its construction, particularly in the use of "come se stesso" which is a literal translation of "come sé medesimo". While the translation is understandable, it lacks the natural flow and idiomaticity that would make it more engaging. The phrase "dovrebbe già cominciare" feels slightly awkward compared to the original's "già cominci a", indicating a somewhat rigid adherence to the source text rather than a smooth adaptation to modern Italian. The translation also misses the opportunity to employ more contemporary expressions that could have made the text more accessible while preserving its essence. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L75" t="n">
+        <v>0.8808</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.6798999999999999</v>
+      </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4231,6 +5155,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian text while maintaining modern readability. The use of "spiegato" for "impaniate" and "in salvo" for "salvamente" shows careful consideration of contemporary language conventions. The phrase "non fugge in salvo" captures the essence of the original's cautionary tone, though it could have been more idiomatically expressed. The term "cinghiale selvatico" is appropriately chosen, reflecting the original's specific reference to wild boar. While the translation is generally accurate and fluent, there is room for improvement in the expression of subtle nuances, such as the original's emphasis on the bird's vulnerability. The syntax flows naturally, though it occasionally leans towards a slightly mechanical construction. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L76" t="n">
+        <v>0.8464</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.6017</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4280,6 +5216,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message in modern Italian. The use of "Io li aprii" instead of "Io gli apersi" shows a nuanced understanding of the subject-object agreement in Italian, while "e loro fuggirono" maintains the original meaning effectively. The phrase "che bisogno c’è" is a natural modern equivalent for "che bisogno è," preserving the rhetorical question form. The translation also appropriately adapts "il tuo cuore" to maintain the intimate tone of the original text. The syntax flows naturally and the vocabulary choices are precise, making it indistinguishable from a translation by a highly qualified human.</t>
         </is>
       </c>
+      <c r="L77" t="n">
+        <v>0.8342000000000001</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.8483000000000001</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.6326000000000001</v>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4329,6 +5277,18 @@
           <t>The translation maintains the basic meaning of the original text but exhibits several issues that make it fall short of excellence. The phrase "stanno così" is a literal translation of "son così," which is less idiomatic than the more natural "sono state così." Additionally, the use of "vivere questa vita" instead of "usare questa vita" loses the original's emphasis on the way of life. The construction "dubiti di andartene" is awkward and lacks the nuance of the original "dubiti tu d'andartene." While comprehensible, the translation shows signs of being overly literal and lacks the smoothness and natural flow expected of a high-quality translation.</t>
         </is>
       </c>
+      <c r="L78" t="n">
+        <v>0.8616</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.6241</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.5752</v>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4374,6 +5334,18 @@
           <t>The translation is generally accurate and comprehensible, capturing the essence of the original text. However, it exhibits some mechanical qualities, particularly in the rendering of "dimorare" as "restare," which is a somewhat literal translation that could have been expressed more naturally as "trattenersi." The phrase "che era incitata" is a direct translation of "incitandola," which makes the text feel slightly mechanical rather than flowing naturally. While the translation conveys the basic meaning, it lacks the nuanced expression that would elevate it to a higher score. The use of "padri coscritti" is appropriate, but the overall construction feels like a translation rather than an original piece of modern Italian prose. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L79" t="n">
+        <v>0.8678</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.7427</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4423,6 +5395,18 @@
           <t>The translation captures the essence of the original text while maintaining modern Italian language conventions. The phrase "a cui" is replaced with the more contemporary "ai quali," which is a suitable adaptation for the modern audience. The term "ventura" is appropriately rendered as "sorte," preserving the original meaning while using a word that is more commonly used today. The syntax flows naturally, and the translation successfully conveys the original's intent without resorting to awkward or archaic constructions. The text remains accessible and clear, demonstrating a good balance between respecting the original's style and adapting it to modern Italian norms.</t>
         </is>
       </c>
+      <c r="L80" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.5669</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4472,6 +5456,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully renders it into modern Italian while maintaining the original meaning. The syntax is natural and fluid, with appropriate use of modern Italian expressions such as "si fecero" instead of "furono fatti." The translation accurately captures the historical context and the numerical reference to 3500 Roman soldiers, which was preserved from the original text. The use of "console" instead of "consolo" shows attention to modern Italian spelling conventions. The text flows smoothly and reads naturally, with no signs of being machine-generated. The translation respects the original's tone and style while making it accessible to contemporary readers.</t>
         </is>
       </c>
+      <c r="L81" t="n">
+        <v>0.8153</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.5511</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.4422</v>
+      </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4521,6 +5517,18 @@
           <t>The translation demonstrates a clear misunderstanding of the original text's meaning. "iscaciati" means "deported" or "expelled," not "rewarded" ("ricompensati"). The phrase "per debito" refers to being expelled due to debt, not "merito." Additionally, "ventura buona" translates to "fortune" or "luck," not "buona sorte." The syntax is awkward and fails to capture the original's archaic style while also introducing incorrect meanings. The translation lacks the necessary precision and accuracy required for a proper rendering of the text, making it unreliable for comprehension and potentially misleading for readers.</t>
         </is>
       </c>
+      <c r="L82" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.5516</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4566,6 +5574,18 @@
           <t>The translation is generally correct and comprehensible, but it shows some mechanical traits. The phrase "le vostre preghiere sono efficaci" is a literal translation of "e' vostri preghieri valsono," which sounds slightly awkward in modern Italian. The use of "ebbe fortuna" instead of "ha avuto la possibilità" is a good choice, but the overall structure of the sentence remains too close to the original archaic form. The translation maintains the basic meaning but lacks the natural flow that would make it indistinguishable from a human translation. While it conveys the essential message, it doesn't fully capture the stylistic nuances of the original text. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L83" t="n">
+        <v>0.8136</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.7459</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4619,6 +5639,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic terms "scherani" and "piusori" have been appropriately replaced with their modern equivalents "sceriffi" and "principi," respectively, preserving the historical context. The phrase structure has been reorganized to fit contemporary Italian language patterns, making it accessible to modern readers. The translation successfully captures the essence of the original text, including the historical setting and the characters' intentions, without resorting to literal translations that might sound awkward in modern Italian. The use of "poiché" instead of "con ciò" shows a nuanced understanding of connecting phrases in modern Italian. The translation is both accurate and natural, demonstrating the ability to convey complex historical narratives in a way that feels authentic to the target language.</t>
         </is>
       </c>
+      <c r="L84" t="n">
+        <v>0.8223</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.5182</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4672,6 +5704,18 @@
           <t>The translation is generally accurate and maintains the basic meaning of the original text, preserving the archaic elements while making them accessible to modern readers. However, there are some minor issues that prevent it from achieving a higher score. The term "discendenza" could have been replaced with a more idiomatic expression such as "nascita" or "origine," which would have better captured the medieval context. Additionally, the phrase "alto prestigio" is a somewhat literal translation of "alto pregio," and while it conveys the general idea, it lacks the nuance of the original term. The syntax is modern and comprehensible, but the slight awkwardness in these choices indicates that the translation, while serviceable, doesn't fully capture the stylistic richness of the original text. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L85" t="n">
+        <v>0.8884</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.8213</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4721,6 +5765,18 @@
           <t>The translation demonstrates a basic understanding of the source text but lacks precision and nuance. The phrase "fu spinta" is a literal translation of "fu impinto," missing the idiomatic meaning of "bagnato." The use of "passaggio" instead of "trapasso" fails to capture the historical context and connotation of the original term. The sentence structure is overly simplified, losing the medieval flavor of the original text. While the translation is comprehensible, it doesn't convey the full richness of the original language and lacks the sophisticated interplay of archaic and modern elements present in the gold translation. The modernization of terms is inconsistent, with some terms being too literal and others being too modern. So the overall score is 3.</t>
         </is>
       </c>
+      <c r="L86" t="n">
+        <v>0.9083</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.8393</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.5827</v>
+      </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4770,6 +5826,18 @@
           <t>The translation is generally correct and comprehensible, but it lacks the nuance and sophistication of the original text. The use of "sull'argine" instead of "in su l'argine" is a slight simplification, and "scappare" is a more colloquial choice than "scampare." The sentence structure is modern but somewhat rigid, and the translation doesn't fully capture the archaic tone of the original. While the basic meaning is preserved, the translation misses some of the stylistic elements that would make it more engaging and natural in modern Italian. The choice of "nel caso" is functional but not optimal, as it could have been expressed more elegantly. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L87" t="n">
+        <v>0.8149</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.6973</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4819,6 +5887,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning while maintaining a modern Italian syntax. The archaic terms "intelligenza" and "universitade" are appropriately rendered as "intelligenza" and "università," respectively, preserving the original's essence. The phrase "sottil vista" is elegantly transformed into "visione sottile," capturing the metaphorical depth of the original. The translation successfully balances modern readability with historical accuracy, though it could have been more precise in conveying the exact nuance of "superata la vastità." The slight deviation from the gold translation in the parenthetical addition of "o della totalità" shows a minor attempt at over-explanation, which, while understandable, slightly detracts from the translation's conciseness.</t>
         </is>
       </c>
+      <c r="L88" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.7892</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.6591</v>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4872,6 +5952,18 @@
           <t>The translation demonstrates a strong grasp of the source text's meaning and conveys it in modern Italian while maintaining readability. The archaic terms have been appropriately modernized, such as "salutazione" for "salutazione" and "lettera" for "pistola," which shows good judgment in choosing contemporary equivalents. The syntax follows modern Italian conventions while preserving the original's logical flow. The translation successfully captures the metaphorical nature of the text, particularly in the comparison between the eye and the salutation. However, there is room for improvement in the expression of the final clause, where the use of "all' stesso modo" could be more elegant, though it remains comprehensible. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L89" t="n">
+        <v>0.8428</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.6336000000000001</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.5195</v>
+      </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4921,6 +6013,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original meaning while maintaining readability in modern Italian. The use of "che erano originari" instead of "di quegli" shows a nuanced understanding of the historical context and the evolution of the language. The phrase "formavano la loro nobile città" effectively captures the original's intent, though it could have been more elegant with "erano nati da." The translation avoids literal translations and presents the text in a way that feels natural to contemporary readers, while still respecting the historical nature of the source material. The choice of "Greci" as a singular noun at the end is appropriate, reflecting the original's style without being overly formal. While there are minor opportunities for improvement in terms of elegance, the translation is largely successful in preserving the semantic nuances and cultural context of the original text.</t>
         </is>
       </c>
+      <c r="L90" t="n">
+        <v>0.8403</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.6006</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4970,6 +6074,18 @@
           <t>The translation is mechanically correct but lacks the nuance and style of the original medieval text. The sentence structure is overly simplified and fails to capture the archaic nature of the source material. The use of "era" instead of "fu" is a modern construction that doesn't reflect the original's formal tone. The translation also omits the word "orgentore," which was a significant part of the original text. While it conveys the basic meaning, it misses the opportunity to maintain the historical authenticity of the text. The modernization of the text is too abrupt and doesn't preserve the medieval flavor of the original. So the overall score is 2.</t>
         </is>
       </c>
+      <c r="L91" t="n">
+        <v>0.8509</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5023,6 +6139,18 @@
           <t>The translation demonstrates a strong grasp of the archaic Italian language and successfully conveys the original message. The syntax is modernized while maintaining the essence of the medieval text. The use of "Poiché" instead of "però" shows a nuanced understanding of the context, and the phrase "saper avere misericordia" captures the original sentiment effectively. The translation flows naturally and reads as if it were originally written in modern Italian, indicating a high level of fluency and accuracy. The preservation of the original's tone and the careful selection of modern equivalents for archaic terms demonstrate excellent translation quality.</t>
         </is>
       </c>
+      <c r="L92" t="n">
+        <v>0.7769</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.5363</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5072,6 +6200,18 @@
           <t>The translation is generally accurate and comprehensible, maintaining the basic meaning of the original text. However, it shows some mechanical traits in its construction, particularly in the use of "quindi" which could have been replaced with a more idiomatic expression such as "perciò" or "in quanto". The term "gentile giovane" is a literal translation of "gentile jovane," which, while understandable, lacks the nuance of the original. The syntax follows a somewhat rigid pattern, making it read less naturally than it could have. While the translation is functional and conveys the essential information, it doesn't fully capture the stylistic richness of the medieval text. So the overall score is 3.</t>
         </is>
       </c>
+      <c r="L93" t="n">
+        <v>0.8526</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5121,6 +6261,18 @@
           <t>The translation is generally correct and comprehensible, maintaining the basic meaning of the original text. However, it shows some mechanical traits in its construction, particularly in the use of "diversa da quella che ha" which feels slightly awkward compared to the more idiomatic "delle altre mogli." The expression "si lamenta perché" is a somewhat literal rendering of the original, while "vorrebbe avere" captures the essence of the desire but lacks the nuance of the original's implied regret. The translation is functional but doesn't fully capture the historical and cultural context of the medieval text, making it read more like a modern, albeit adequate, translation rather than a refined one.</t>
         </is>
       </c>
+      <c r="L94" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.8742</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.6385999999999999</v>
+      </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5170,6 +6322,18 @@
           <t>The translation is generally correct and comprehensible, but it exhibits several issues that prevent it from achieving a higher score. The phrase "cui fu mostrato" is a literal translation of "essendogli mostrato," which sounds somewhat mechanical and lacks the elegance of the original. Additionally, the use of quotation marks around "Uccidi e mangia" is unnecessary and breaks the flow of the text. While the translation conveys the basic meaning, it fails to capture the poetic and archaic nature of the original text, making it read more like a modern, direct translation rather than a nuanced rendering of the medieval language. The syntax is functional but lacks the sophistication expected in a high-quality translation.</t>
         </is>
       </c>
+      <c r="L95" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.6953</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.5983000000000001</v>
+      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -5215,6 +6379,18 @@
           <t>The translation demonstrates a strong grasp of the original text's meaning and successfully renders it into modern Italian while maintaining readability. The archaic terms are appropriately replaced with their modern equivalents, such as "pregollo" becoming "chiese" and "ubbligato" becoming "vincolato." The syntax flows naturally, and the translation captures the essence of the original text without feeling overly mechanical. However, there are minor areas where the translation could have been more elegant, particularly in the rendering of "el gentile uomo," which could have been expressed more idiomatically. The translation also slightly simplifies the original's tone, though this is acceptable given the task of modernizing the text. So the overall score is 4.</t>
         </is>
       </c>
+      <c r="L96" t="n">
+        <v>0.8485</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.7417</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5264,6 +6440,18 @@
           <t>The translation maintains the archaic tone of the original text while successfully adapting it to modern Italian. The use of "Che cosa rappresentiamo" instead of "figuriamo" shows a nuanced understanding of the original's rhetorical style. The phrase "quel popolo" effectively replaces "il qual populo," preserving the original's flow while using contemporary language. The syntax is modern yet respectful of the source content, and the text flows naturally without feeling machine-generated. The translation captures the semantic nuances of the original, including the metaphorical use of "Aquilone" and the concept of "popolo Gentile." The modernization of terms such as "popolo" and "giogo" is done with precision, maintaining the original's meaning while making it accessible to contemporary readers.</t>
         </is>
       </c>
+      <c r="L97" t="n">
+        <v>0.8469</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.7383</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.6377</v>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5313,6 +6501,18 @@
           <t>The translation captures the essence of the original text but exhibits several issues that prevent it from achieving a higher score. While the basic meaning is preserved, the use of "perché" instead of "ch'io non lo sofferrò e non lo lascerò" introduces a logical connection that wasn't present in the original, altering the intended message. Additionally, the phrase "non puoi più a lungo dimorare" is a direct translation that lacks the idiomaticity of the original, making it sound somewhat mechanical. The translation also fails to maintain the archaic tone of the original, which was a key element of the source text. The sentence structure is overly simplified compared to the original's complexity, resulting in a loss of nuance and stylistic richness. So the overall score is 3.</t>
         </is>
       </c>
+      <c r="L98" t="n">
+        <v>0.8074</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.7847</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.7167</v>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
